--- a/output/pdf_financials_xlsx/ANTL.xlsx
+++ b/output/pdf_financials_xlsx/ANTL.xlsx
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.267224</v>
+        <v>-0.267224</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.874644</v>
+        <v>-0.874644</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>0.993707</v>
@@ -979,13 +979,13 @@
         <v>4.485501</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.130492</v>
+        <v>-1.130492</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.98603</v>
+        <v>-0.98603</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.964708</v>
+        <v>-0.964708</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-0.7983130000000001</v>
@@ -1010,10 +1010,10 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.034</v>
+        <v>-1.953414</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>-8.971002</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -1155,25 +1155,25 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.267224</v>
+        <v>-0.267224</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.874644</v>
+        <v>-0.874644</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.959707</v>
+        <v>-0.959707</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>4.485501</v>
+        <v>-4.485501</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.130492</v>
+        <v>-1.130492</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.98603</v>
+        <v>-0.98603</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.964708</v>
+        <v>-0.964708</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-0.7983130000000001</v>
@@ -1266,25 +1266,25 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.267224</v>
+        <v>-0.267224</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.874644</v>
+        <v>-0.874644</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.959707</v>
+        <v>-0.959707</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>4.485501</v>
+        <v>-4.485501</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.130492</v>
+        <v>-1.130492</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.98603</v>
+        <v>-0.98603</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.964708</v>
+        <v>-0.964708</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-0.7983130000000001</v>
@@ -1377,25 +1377,25 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-15.719059</v>
+        <v>15.719059</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-39.756545</v>
+        <v>39.756545</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-43.623045</v>
+        <v>43.623045</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-45.770418</v>
+        <v>45.770418</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-56.5246</v>
+        <v>56.5246</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-61.626875</v>
+        <v>61.626875</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-74.208308</v>
+        <v>74.208308</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.267224</v>
+        <v>-0.267224</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.874644</v>
+        <v>-0.874644</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>0.993707</v>
@@ -1430,13 +1430,13 @@
         <v>4.485501</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.130492</v>
+        <v>-1.130492</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.98603</v>
+        <v>-0.98603</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.964708</v>
+        <v>-0.964708</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.7983130000000001</v>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.267224</v>
+        <v>-0.267224</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.874644</v>
+        <v>-0.874644</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0.993707</v>
@@ -1504,13 +1504,13 @@
         <v>4.485501</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.130492</v>
+        <v>-1.130492</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.986308</v>
+        <v>-0.985752</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.966329</v>
+        <v>-0.963087</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.796088</v>
@@ -1586,25 +1586,25 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.421531698981692</v>
+        <v>196.5784683010183</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -12640,28 +12640,28 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0.267224</v>
+        <v>-0.267224</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>0.874644</v>
+        <v>-0.874644</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.959707</v>
+        <v>-0.959707</v>
       </c>
       <c r="H114" s="5" t="n">
-        <v>4.485501</v>
+        <v>-4.485501</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>1.130492</v>
+        <v>-1.130492</v>
       </c>
       <c r="J114" s="5" t="n">
-        <v>0.98603</v>
+        <v>-0.98603</v>
       </c>
       <c r="K114" s="5" t="n">
-        <v>0.964708</v>
+        <v>-0.964708</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>0.7983130000000001</v>
+        <v>-0.7983130000000001</v>
       </c>
       <c r="M114" s="5" t="n">
         <v>-0.775405</v>
@@ -15046,7 +15046,7 @@
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>0.267224</v>
+        <v>-0.267224</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ANTL.xlsx
+++ b/output/pdf_financials_xlsx/ANTL.xlsx
@@ -1687,34 +1687,34 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.08437</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.277858</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.606773</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.030017</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.667955</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.338511</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.639856</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.344208</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.012424</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.005831</v>
       </c>
     </row>
     <row r="35">
@@ -1761,34 +1761,34 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.08437</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.277858</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.606773</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.030017</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.667955</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.338511</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.639856</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.344208</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.012424</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.005831</v>
       </c>
     </row>
     <row r="37">
@@ -2205,34 +2205,34 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.179301</v>
+        <v>0.094931</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.467045</v>
+        <v>0.189187</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.685328</v>
+        <v>0.078555</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.07745</v>
+        <v>0.047433</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.744199</v>
+        <v>0.07624400000000001</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.448584</v>
+        <v>0.110073</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.693845</v>
+        <v>0.053989</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.408086</v>
+        <v>0.063878</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.080652</v>
+        <v>0.068228</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.050953</v>
+        <v>0.045122</v>
       </c>
     </row>
     <row r="49">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/ANTL.xlsx
+++ b/output/pdf_financials_xlsx/ANTL.xlsx
@@ -5009,13 +5009,13 @@
         <v>0</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>0</v>
+        <v>3.384415</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0</v>
+        <v>0.491704</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>0</v>
+        <v>1.129464</v>
       </c>
       <c r="I120" s="3" t="n">
         <v>0</v>
@@ -10106,7 +10106,11 @@
           <t>Proceeds from issuance of common shares – net of issuance costs</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ANTL.xlsx
+++ b/output/pdf_financials_xlsx/ANTL.xlsx
@@ -970,7 +970,7 @@
         <v>-0.267224</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-0.874644</v>
+        <v>-1.066644</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>0.993707</v>
@@ -1007,10 +1007,10 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>0.192</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-1.953414</v>
+        <v>0.034</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-8.971002</v>
@@ -1421,7 +1421,7 @@
         <v>-0.267224</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.874644</v>
+        <v>-1.066644</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>0.993707</v>
@@ -1495,7 +1495,7 @@
         <v>-0.267224</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.874644</v>
+        <v>-1.066644</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0.993707</v>
@@ -1589,10 +1589,10 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-18.0003825081283</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>196.5784683010183</v>
+        <v>3.421531698981692</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>200</v>
@@ -4679,16 +4679,16 @@
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.046938</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.007543</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006011</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001331</v>
       </c>
       <c r="K111" s="3" t="n">
         <v>0</v>
@@ -5556,16 +5556,16 @@
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.046938</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.007543</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006011</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001331</v>
       </c>
       <c r="K134" s="3" t="n">
         <v>0</v>
@@ -5595,13 +5595,13 @@
         <v>-0.650675</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.363665</v>
+        <v>-0.410603</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-0.626845</v>
+        <v>-0.634388</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-0.603867</v>
+        <v>-0.609878</v>
       </c>
       <c r="J135" s="1" t="inlineStr">
         <is>
@@ -8688,7 +8688,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -14590,7 +14594,11 @@
           <t>Income tax recovery (note 11)</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -14850,7 +14858,11 @@
           <t>Income tax recovery (note 9)</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
